--- a/eval-suite/cases/010_dwb_user_profile_f/mapping.xlsx
+++ b/eval-suite/cases/010_dwb_user_profile_f/mapping.xlsx
@@ -2,40 +2,387 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24980" windowHeight="11800" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="实体级mapping" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="属性级mapping" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="22">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="34">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2563EB"/>
+        <bgColor rgb="FF2563EB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -43,15 +390,329 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -404,7 +1065,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -414,243 +1074,313 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:M5"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="4"/>
+  <cols>
+    <col width="14" customWidth="1" min="3" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>源表schema</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>源表物理表名</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>分组</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>源表schema*</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>源表中文名</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>源表别名</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>目标表schema</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>源表物理表名*</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>源表别名*</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>目标表逻辑schema*</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>目标表中文名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>目标表物理表名</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>目标表物理名称*</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>取数规则</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>关联&amp;限定条件</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>数据库类型</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>ods</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>用户基础信息表</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>ods_user_basic_f</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>用户基础信息表</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>oub</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>用户画像宽表</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>dwb_user_profile_f</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
         <is>
           <t>主表</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>场景1-用户基础信息</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>用户等级维度表</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>dim_user_level_d</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>用户等级维度表</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>dul</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>用户画像宽表</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>dwb_user_profile_f</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
         <is>
           <t>LEFT JOIN ON u.level_id = l.level_id</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>场景1-等级信息</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="31" customHeight="1">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>地区维度表</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
         <is>
           <t>dim_region_d</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>地区维度表</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>drd</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>用户画像宽表</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>dwb_user_profile_f</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
         <is>
           <t>LEFT JOIN ON u.province_code = r.region_code</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>场景1-地区信息</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>dim</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>用户来源维度表</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
         <is>
           <t>dim_user_source_d</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>用户来源维度表</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>dus</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>slusr</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>用户画像宽表</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>dwb_user_profile_f</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>LEFT JOIN ON u.source_id = s.source_id</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>场景1-来源渠道</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -663,82 +1393,96 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N188"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:O188"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="14" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="45" customWidth="1" min="18" max="18"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+    <row r="1" ht="31" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>源Schema</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>源表物理表名</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>源表物理表别名</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>源表字段中文名</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>源表字段名</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>源表字段类型</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>映射规则*</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>映射表达式</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>目标字段名*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>目标字段中文名</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>目标字段类型</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
-    </row>
-    <row r="2">
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>数据标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="31" customHeight="1">
       <c r="A2" t="n">
         <v>1</v>
       </c>
@@ -807,8 +1551,9 @@
           <t>主键</t>
         </is>
       </c>
-    </row>
-    <row r="3">
+      <c r="O2" t="inlineStr"/>
+    </row>
+    <row r="3" ht="31" customHeight="1">
       <c r="A3" t="n">
         <v>2</v>
       </c>
@@ -873,8 +1618,9 @@
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
-    </row>
-    <row r="4">
+      <c r="O3" t="inlineStr"/>
+    </row>
+    <row r="4" ht="46" customHeight="1">
       <c r="A4" t="n">
         <v>3</v>
       </c>
@@ -939,8 +1685,9 @@
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
-    </row>
-    <row r="5">
+      <c r="O4" t="inlineStr"/>
+    </row>
+    <row r="5" ht="76" customHeight="1">
       <c r="A5" t="n">
         <v>4</v>
       </c>
@@ -1005,8 +1752,9 @@
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
-    </row>
-    <row r="6">
+      <c r="O5" t="inlineStr"/>
+    </row>
+    <row r="6" ht="122" customHeight="1">
       <c r="A6" t="n">
         <v>5</v>
       </c>
@@ -1071,8 +1819,9 @@
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
-    </row>
-    <row r="7">
+      <c r="O6" t="inlineStr"/>
+    </row>
+    <row r="7" ht="122" customHeight="1">
       <c r="A7" t="n">
         <v>6</v>
       </c>
@@ -1137,8 +1886,9 @@
         </is>
       </c>
       <c r="N7" t="inlineStr"/>
-    </row>
-    <row r="8">
+      <c r="O7" t="inlineStr"/>
+    </row>
+    <row r="8" ht="122" customHeight="1">
       <c r="A8" t="n">
         <v>7</v>
       </c>
@@ -1203,8 +1953,9 @@
         </is>
       </c>
       <c r="N8" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="O8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="122" customHeight="1">
       <c r="A9" t="n">
         <v>8</v>
       </c>
@@ -1269,8 +2020,9 @@
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
-    </row>
-    <row r="10">
+      <c r="O9" t="inlineStr"/>
+    </row>
+    <row r="10" ht="46" customHeight="1">
       <c r="A10" t="n">
         <v>9</v>
       </c>
@@ -1335,8 +2087,9 @@
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
-    </row>
-    <row r="11">
+      <c r="O10" t="inlineStr"/>
+    </row>
+    <row r="11" ht="137" customHeight="1">
       <c r="A11" t="n">
         <v>10</v>
       </c>
@@ -1401,8 +2154,9 @@
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
-    </row>
-    <row r="12">
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12" ht="152" customHeight="1">
       <c r="A12" t="n">
         <v>11</v>
       </c>
@@ -1467,8 +2221,9 @@
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
-    </row>
-    <row r="13">
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13" ht="76" customHeight="1">
       <c r="A13" t="n">
         <v>12</v>
       </c>
@@ -1533,6 +2288,7 @@
         </is>
       </c>
       <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1599,6 +2355,7 @@
         </is>
       </c>
       <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1665,6 +2422,7 @@
         </is>
       </c>
       <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1731,6 +2489,7 @@
         </is>
       </c>
       <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1797,6 +2556,7 @@
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1863,6 +2623,7 @@
         </is>
       </c>
       <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1929,6 +2690,7 @@
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1995,6 +2757,7 @@
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2061,6 +2824,7 @@
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2127,6 +2891,7 @@
         </is>
       </c>
       <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2193,6 +2958,7 @@
         </is>
       </c>
       <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2259,6 +3025,7 @@
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2325,6 +3092,7 @@
         </is>
       </c>
       <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2391,6 +3159,7 @@
         </is>
       </c>
       <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2457,6 +3226,7 @@
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2523,6 +3293,7 @@
         </is>
       </c>
       <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2589,6 +3360,7 @@
         </is>
       </c>
       <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2655,6 +3427,7 @@
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2721,6 +3494,7 @@
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2787,6 +3561,7 @@
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
+      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2853,6 +3628,7 @@
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
+      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -2919,6 +3695,7 @@
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
+      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -2985,6 +3762,7 @@
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3051,6 +3829,7 @@
         </is>
       </c>
       <c r="N36" t="inlineStr"/>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3117,6 +3896,7 @@
         </is>
       </c>
       <c r="N37" t="inlineStr"/>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3183,6 +3963,7 @@
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -3249,6 +4030,7 @@
         </is>
       </c>
       <c r="N39" t="inlineStr"/>
+      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -3315,6 +4097,7 @@
         </is>
       </c>
       <c r="N40" t="inlineStr"/>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -3381,6 +4164,7 @@
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
+      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -3447,6 +4231,7 @@
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
+      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -3513,6 +4298,7 @@
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -3579,6 +4365,7 @@
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
+      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -3645,6 +4432,7 @@
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
+      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -3711,6 +4499,7 @@
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
+      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -3777,6 +4566,7 @@
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
+      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -3843,6 +4633,7 @@
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -3909,6 +4700,7 @@
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -3975,6 +4767,7 @@
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4041,6 +4834,7 @@
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4107,6 +4901,7 @@
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4173,6 +4968,7 @@
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -4239,6 +5035,7 @@
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -4305,6 +5102,7 @@
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -4371,6 +5169,7 @@
         </is>
       </c>
       <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -4437,6 +5236,7 @@
         </is>
       </c>
       <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -4503,6 +5303,7 @@
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -4569,6 +5370,7 @@
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -4635,6 +5437,7 @@
         </is>
       </c>
       <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -4701,6 +5504,7 @@
         </is>
       </c>
       <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -4767,6 +5571,7 @@
         </is>
       </c>
       <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4833,6 +5638,7 @@
         </is>
       </c>
       <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -4899,6 +5705,7 @@
         </is>
       </c>
       <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -4965,6 +5772,7 @@
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
+      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5031,6 +5839,7 @@
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
+      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5097,6 +5906,7 @@
         </is>
       </c>
       <c r="N67" t="inlineStr"/>
+      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5163,6 +5973,7 @@
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
+      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -5229,6 +6040,7 @@
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
+      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -5295,6 +6107,7 @@
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -5361,6 +6174,7 @@
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
+      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -5427,6 +6241,7 @@
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
+      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -5493,6 +6308,7 @@
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
+      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -5559,6 +6375,7 @@
         </is>
       </c>
       <c r="N74" t="inlineStr"/>
+      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -5625,6 +6442,7 @@
         </is>
       </c>
       <c r="N75" t="inlineStr"/>
+      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -5691,6 +6509,7 @@
         </is>
       </c>
       <c r="N76" t="inlineStr"/>
+      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -5757,6 +6576,7 @@
         </is>
       </c>
       <c r="N77" t="inlineStr"/>
+      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -5823,6 +6643,7 @@
         </is>
       </c>
       <c r="N78" t="inlineStr"/>
+      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -5889,6 +6710,7 @@
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
+      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -5955,6 +6777,7 @@
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
+      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6021,6 +6844,7 @@
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
+      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6087,6 +6911,7 @@
         </is>
       </c>
       <c r="N82" t="inlineStr"/>
+      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6153,6 +6978,7 @@
         </is>
       </c>
       <c r="N83" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -6219,6 +7045,7 @@
         </is>
       </c>
       <c r="N84" t="inlineStr"/>
+      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -6285,6 +7112,7 @@
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
+      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -6351,6 +7179,7 @@
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
+      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -6417,6 +7246,7 @@
         </is>
       </c>
       <c r="N87" t="inlineStr"/>
+      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -6483,6 +7313,7 @@
         </is>
       </c>
       <c r="N88" t="inlineStr"/>
+      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -6549,6 +7380,7 @@
         </is>
       </c>
       <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -6615,6 +7447,7 @@
         </is>
       </c>
       <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -6681,6 +7514,7 @@
         </is>
       </c>
       <c r="N91" t="inlineStr"/>
+      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -6747,6 +7581,7 @@
         </is>
       </c>
       <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -6813,6 +7648,7 @@
         </is>
       </c>
       <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -6879,6 +7715,7 @@
         </is>
       </c>
       <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -6945,6 +7782,7 @@
         </is>
       </c>
       <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7011,6 +7849,7 @@
         </is>
       </c>
       <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7077,6 +7916,7 @@
         </is>
       </c>
       <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7143,6 +7983,7 @@
         </is>
       </c>
       <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -7209,6 +8050,7 @@
         </is>
       </c>
       <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -7275,6 +8117,7 @@
         </is>
       </c>
       <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -7341,6 +8184,7 @@
         </is>
       </c>
       <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -7407,6 +8251,7 @@
         </is>
       </c>
       <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -7473,6 +8318,7 @@
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -7539,6 +8385,7 @@
         </is>
       </c>
       <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -7605,6 +8452,7 @@
         </is>
       </c>
       <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -7671,6 +8519,7 @@
         </is>
       </c>
       <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -7737,6 +8586,7 @@
         </is>
       </c>
       <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -7803,6 +8653,7 @@
         </is>
       </c>
       <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -7869,6 +8720,7 @@
         </is>
       </c>
       <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -7935,6 +8787,7 @@
         </is>
       </c>
       <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8001,6 +8854,7 @@
         </is>
       </c>
       <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8067,6 +8921,7 @@
         </is>
       </c>
       <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8133,6 +8988,7 @@
         </is>
       </c>
       <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -8199,6 +9055,7 @@
         </is>
       </c>
       <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -8265,6 +9122,7 @@
         </is>
       </c>
       <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -8331,6 +9189,7 @@
         </is>
       </c>
       <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -8397,6 +9256,7 @@
         </is>
       </c>
       <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -8463,6 +9323,7 @@
         </is>
       </c>
       <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -8529,6 +9390,7 @@
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -8595,6 +9457,7 @@
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -8661,6 +9524,7 @@
         </is>
       </c>
       <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -8727,6 +9591,7 @@
         </is>
       </c>
       <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -8793,6 +9658,7 @@
         </is>
       </c>
       <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -8859,6 +9725,7 @@
         </is>
       </c>
       <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -8925,6 +9792,7 @@
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -8991,6 +9859,7 @@
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9057,6 +9926,7 @@
         </is>
       </c>
       <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9123,6 +9993,7 @@
         </is>
       </c>
       <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -9189,6 +10060,7 @@
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -9255,6 +10127,7 @@
         </is>
       </c>
       <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -9321,6 +10194,7 @@
         </is>
       </c>
       <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -9387,6 +10261,7 @@
         </is>
       </c>
       <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -9453,6 +10328,7 @@
         </is>
       </c>
       <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -9519,6 +10395,7 @@
         </is>
       </c>
       <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -9585,6 +10462,7 @@
         </is>
       </c>
       <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -9651,6 +10529,7 @@
         </is>
       </c>
       <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -9717,6 +10596,7 @@
         </is>
       </c>
       <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -9783,6 +10663,7 @@
         </is>
       </c>
       <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -9849,6 +10730,7 @@
         </is>
       </c>
       <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -9915,6 +10797,7 @@
         </is>
       </c>
       <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -9981,6 +10864,7 @@
         </is>
       </c>
       <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10047,6 +10931,7 @@
         </is>
       </c>
       <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10113,6 +10998,7 @@
         </is>
       </c>
       <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -10179,6 +11065,7 @@
         </is>
       </c>
       <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -10245,6 +11132,7 @@
         </is>
       </c>
       <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -10311,6 +11199,7 @@
         </is>
       </c>
       <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -10377,6 +11266,7 @@
         </is>
       </c>
       <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -10443,6 +11333,7 @@
         </is>
       </c>
       <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -10509,6 +11400,7 @@
         </is>
       </c>
       <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -10575,6 +11467,7 @@
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -10641,6 +11534,7 @@
         </is>
       </c>
       <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -10707,6 +11601,7 @@
         </is>
       </c>
       <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -10773,6 +11668,7 @@
         </is>
       </c>
       <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -10839,6 +11735,7 @@
         </is>
       </c>
       <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -10905,6 +11802,7 @@
         </is>
       </c>
       <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -10971,6 +11869,7 @@
         </is>
       </c>
       <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -11037,6 +11936,7 @@
         </is>
       </c>
       <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -11103,6 +12003,7 @@
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -11169,6 +12070,7 @@
         </is>
       </c>
       <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -11235,6 +12137,7 @@
         </is>
       </c>
       <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -11301,6 +12204,7 @@
         </is>
       </c>
       <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -11367,6 +12271,7 @@
         </is>
       </c>
       <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -11433,6 +12338,7 @@
         </is>
       </c>
       <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -11499,6 +12405,7 @@
         </is>
       </c>
       <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -11565,6 +12472,7 @@
         </is>
       </c>
       <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -11631,6 +12539,7 @@
         </is>
       </c>
       <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -11697,6 +12606,7 @@
         </is>
       </c>
       <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -11763,6 +12673,7 @@
         </is>
       </c>
       <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -11829,6 +12740,7 @@
         </is>
       </c>
       <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -11895,6 +12807,7 @@
         </is>
       </c>
       <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -11961,6 +12874,7 @@
         </is>
       </c>
       <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -12027,6 +12941,7 @@
         </is>
       </c>
       <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -12093,6 +13008,7 @@
         </is>
       </c>
       <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -12159,6 +13075,7 @@
         </is>
       </c>
       <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -12225,6 +13142,7 @@
         </is>
       </c>
       <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -12291,6 +13209,7 @@
         </is>
       </c>
       <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -12357,6 +13276,7 @@
         </is>
       </c>
       <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -12423,6 +13343,7 @@
         </is>
       </c>
       <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -12489,6 +13410,7 @@
         </is>
       </c>
       <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -12555,6 +13477,7 @@
         </is>
       </c>
       <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -12621,6 +13544,7 @@
         </is>
       </c>
       <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -12687,6 +13611,7 @@
         </is>
       </c>
       <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -12753,6 +13678,7 @@
         </is>
       </c>
       <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -12819,6 +13745,7 @@
         </is>
       </c>
       <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -12865,6 +13792,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -12911,6 +13839,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -12957,6 +13886,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -13003,6 +13933,7 @@
           <t>审计字段</t>
         </is>
       </c>
+      <c r="O188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eval-suite/cases/010_dwb_user_profile_f/mapping.xlsx
+++ b/eval-suite/cases/010_dwb_user_profile_f/mapping.xlsx
@@ -1195,10 +1195,9 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>dwb_user_profile_f</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>dwb_user_profile_i</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
           <t>主表</t>
@@ -1209,7 +1208,6 @@
           <t>场景1-用户基础信息</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1252,10 +1250,9 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>dwb_user_profile_f</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr"/>
+          <t>dwb_user_profile_i</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr">
         <is>
           <t>LEFT JOIN ON u.level_id = l.level_id</t>
@@ -1266,7 +1263,6 @@
           <t>场景1-等级信息</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4" ht="31" customHeight="1">
       <c r="A4" t="n">
@@ -1309,10 +1305,9 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>dwb_user_profile_f</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
+          <t>dwb_user_profile_i</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>LEFT JOIN ON u.province_code = r.region_code</t>
@@ -1323,7 +1318,6 @@
           <t>场景1-地区信息</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1366,10 +1360,9 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>dwb_user_profile_f</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
+          <t>dwb_user_profile_i</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>LEFT JOIN ON u.source_id = s.source_id</t>
@@ -1380,7 +1373,6 @@
           <t>场景1-来源渠道</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1551,7 +1543,6 @@
           <t>主键</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3" ht="31" customHeight="1">
       <c r="A3" t="n">
@@ -1617,8 +1608,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4" ht="46" customHeight="1">
       <c r="A4" t="n">
@@ -1684,8 +1673,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5" ht="76" customHeight="1">
       <c r="A5" t="n">
@@ -1751,8 +1738,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6" ht="122" customHeight="1">
       <c r="A6" t="n">
@@ -1818,8 +1803,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7" ht="122" customHeight="1">
       <c r="A7" t="n">
@@ -1885,8 +1868,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8" ht="122" customHeight="1">
       <c r="A8" t="n">
@@ -1952,8 +1933,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9" ht="122" customHeight="1">
       <c r="A9" t="n">
@@ -2019,8 +1998,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10" ht="46" customHeight="1">
       <c r="A10" t="n">
@@ -2086,8 +2063,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11" ht="137" customHeight="1">
       <c r="A11" t="n">
@@ -2153,8 +2128,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12" ht="152" customHeight="1">
       <c r="A12" t="n">
@@ -2220,8 +2193,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13" ht="76" customHeight="1">
       <c r="A13" t="n">
@@ -2287,8 +2258,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2354,8 +2323,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2421,8 +2388,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2488,8 +2453,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2555,8 +2518,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2622,8 +2583,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2689,8 +2648,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2756,8 +2713,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2823,8 +2778,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2890,8 +2843,6 @@
           <t>date</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2957,8 +2908,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3024,8 +2973,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3091,8 +3038,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3158,8 +3103,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3225,8 +3168,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3292,8 +3233,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3359,8 +3298,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3426,8 +3363,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3493,8 +3428,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3560,8 +3493,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3627,8 +3558,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3694,8 +3623,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3761,8 +3688,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -3828,8 +3753,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -3895,8 +3818,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -3962,8 +3883,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4029,8 +3948,6 @@
           <t>decimal(10,6)</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4096,8 +4013,6 @@
           <t>decimal(10,6)</t>
         </is>
       </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4163,8 +4078,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4230,8 +4143,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4297,8 +4208,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4364,8 +4273,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4431,8 +4338,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -4498,8 +4403,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -4565,8 +4468,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -4632,8 +4533,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -4699,8 +4598,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -4766,8 +4663,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -4833,8 +4728,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -4900,8 +4793,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -4967,8 +4858,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5034,8 +4923,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5101,8 +4988,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -5168,8 +5053,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -5235,8 +5118,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -5302,8 +5183,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -5369,8 +5248,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -5436,8 +5313,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -5503,8 +5378,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -5570,8 +5443,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -5637,8 +5508,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -5704,8 +5573,6 @@
           <t>varchar(1000)</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -5771,8 +5638,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -5838,8 +5703,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -5905,8 +5768,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -5972,8 +5833,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -6039,8 +5898,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -6106,8 +5963,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6173,8 +6028,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -6240,8 +6093,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -6307,8 +6158,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -6374,8 +6223,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -6441,8 +6288,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -6508,8 +6353,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -6575,8 +6418,6 @@
           <t>varchar(1000)</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -6642,8 +6483,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -6709,8 +6548,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -6776,8 +6613,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -6843,8 +6678,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -6910,8 +6743,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -6977,8 +6808,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -7044,8 +6873,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -7111,8 +6938,6 @@
           <t>timestamp</t>
         </is>
       </c>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -7178,8 +7003,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -7245,8 +7068,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -7312,8 +7133,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -7379,8 +7198,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -7446,8 +7263,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -7513,8 +7328,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -7580,8 +7393,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -7647,8 +7458,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -7714,8 +7523,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N94" t="inlineStr"/>
-      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -7781,8 +7588,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N95" t="inlineStr"/>
-      <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -7848,8 +7653,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N96" t="inlineStr"/>
-      <c r="O96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -7915,8 +7718,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N97" t="inlineStr"/>
-      <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -7982,8 +7783,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N98" t="inlineStr"/>
-      <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -8049,8 +7848,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N99" t="inlineStr"/>
-      <c r="O99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -8116,8 +7913,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N100" t="inlineStr"/>
-      <c r="O100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -8183,8 +7978,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N101" t="inlineStr"/>
-      <c r="O101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -8250,8 +8043,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N102" t="inlineStr"/>
-      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -8317,8 +8108,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N103" t="inlineStr"/>
-      <c r="O103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -8384,8 +8173,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N104" t="inlineStr"/>
-      <c r="O104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -8451,8 +8238,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N105" t="inlineStr"/>
-      <c r="O105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -8518,8 +8303,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N106" t="inlineStr"/>
-      <c r="O106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -8585,8 +8368,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N107" t="inlineStr"/>
-      <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -8652,8 +8433,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N108" t="inlineStr"/>
-      <c r="O108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -8719,8 +8498,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N109" t="inlineStr"/>
-      <c r="O109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -8786,8 +8563,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -8853,8 +8628,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -8920,8 +8693,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -8987,8 +8758,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -9054,8 +8823,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -9121,8 +8888,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -9188,8 +8953,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -9255,8 +9018,6 @@
           <t>decimal(10,6)</t>
         </is>
       </c>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -9322,8 +9083,6 @@
           <t>decimal(10,6)</t>
         </is>
       </c>
-      <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -9389,8 +9148,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -9456,8 +9213,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -9523,8 +9278,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -9590,8 +9343,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -9657,8 +9408,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -9724,8 +9473,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N124" t="inlineStr"/>
-      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -9791,8 +9538,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -9858,8 +9603,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -9925,8 +9668,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -9992,8 +9733,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -10059,8 +9798,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -10126,8 +9863,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -10193,8 +9928,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -10260,8 +9993,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -10327,8 +10058,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -10394,8 +10123,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -10461,8 +10188,6 @@
           <t>varchar(10)</t>
         </is>
       </c>
-      <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -10528,8 +10253,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -10595,8 +10318,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -10662,8 +10383,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -10729,8 +10448,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -10796,8 +10513,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -10863,8 +10578,6 @@
           <t>varchar(20)</t>
         </is>
       </c>
-      <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -10930,8 +10643,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -10997,8 +10708,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -11064,8 +10773,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -11131,8 +10838,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -11198,8 +10903,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -11265,8 +10968,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -11332,8 +11033,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -11399,8 +11098,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -11466,8 +11163,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -11533,8 +11228,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -11600,8 +11293,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -11667,8 +11358,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -11734,8 +11423,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N154" t="inlineStr"/>
-      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -11801,8 +11488,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr"/>
-      <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -11868,8 +11553,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N156" t="inlineStr"/>
-      <c r="O156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -11935,8 +11618,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -12002,8 +11683,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -12069,8 +11748,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -12136,8 +11813,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -12203,8 +11878,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -12270,8 +11943,6 @@
           <t>varchar(500)</t>
         </is>
       </c>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -12337,8 +12008,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -12404,8 +12073,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -12471,8 +12138,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N165" t="inlineStr"/>
-      <c r="O165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -12538,8 +12203,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N166" t="inlineStr"/>
-      <c r="O166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -12605,8 +12268,6 @@
           <t>varchar(100)</t>
         </is>
       </c>
-      <c r="N167" t="inlineStr"/>
-      <c r="O167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -12672,8 +12333,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N168" t="inlineStr"/>
-      <c r="O168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -12739,8 +12398,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N169" t="inlineStr"/>
-      <c r="O169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -12806,8 +12463,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N170" t="inlineStr"/>
-      <c r="O170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -12873,8 +12528,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
-      <c r="O171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -12940,8 +12593,6 @@
           <t>decimal(5,2)</t>
         </is>
       </c>
-      <c r="N172" t="inlineStr"/>
-      <c r="O172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -13007,8 +12658,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N173" t="inlineStr"/>
-      <c r="O173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -13074,8 +12723,6 @@
           <t>decimal(18,2)</t>
         </is>
       </c>
-      <c r="N174" t="inlineStr"/>
-      <c r="O174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -13141,8 +12788,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N175" t="inlineStr"/>
-      <c r="O175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -13208,8 +12853,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N176" t="inlineStr"/>
-      <c r="O176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -13275,8 +12918,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N177" t="inlineStr"/>
-      <c r="O177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -13342,8 +12983,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N178" t="inlineStr"/>
-      <c r="O178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -13409,8 +13048,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N179" t="inlineStr"/>
-      <c r="O179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -13476,8 +13113,6 @@
           <t>varchar(200)</t>
         </is>
       </c>
-      <c r="N180" t="inlineStr"/>
-      <c r="O180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -13543,8 +13178,6 @@
           <t>varchar(50)</t>
         </is>
       </c>
-      <c r="N181" t="inlineStr"/>
-      <c r="O181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -13610,8 +13243,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N182" t="inlineStr"/>
-      <c r="O182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -13677,8 +13308,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N183" t="inlineStr"/>
-      <c r="O183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -13744,8 +13373,6 @@
           <t>int</t>
         </is>
       </c>
-      <c r="N184" t="inlineStr"/>
-      <c r="O184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -13756,12 +13383,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
       <c r="I185" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -13792,7 +13413,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -13803,12 +13423,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C186" t="inlineStr"/>
-      <c r="D186" t="inlineStr"/>
-      <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
-      <c r="H186" t="inlineStr"/>
       <c r="I186" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -13839,7 +13453,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -13850,12 +13463,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr"/>
-      <c r="D187" t="inlineStr"/>
-      <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr"/>
-      <c r="G187" t="inlineStr"/>
-      <c r="H187" t="inlineStr"/>
       <c r="I187" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -13886,7 +13493,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -13897,12 +13503,6 @@
           <t>default</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
       <c r="I188" t="inlineStr">
         <is>
           <t>赋值</t>
@@ -13933,7 +13533,6 @@
           <t>审计字段</t>
         </is>
       </c>
-      <c r="O188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/eval-suite/cases/010_dwb_user_profile_f/mapping.xlsx
+++ b/eval-suite/cases/010_dwb_user_profile_f/mapping.xlsx
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>源表物理表别名</t>
+          <t>源表别名</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
